--- a/artfynd/A 51036-2022 artfynd.xlsx
+++ b/artfynd/A 51036-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51036-2022 artfynd.xlsx
+++ b/artfynd/A 51036-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>16612609</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492162.2557566825</v>
+        <v>492162</v>
       </c>
       <c r="R2" t="n">
-        <v>6609348.421983986</v>
+        <v>6609348</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -751,19 +746,9 @@
           <t>1980-08-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1980-08-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -798,16 +783,11 @@
         <v>80476233</v>
       </c>
       <c r="B3" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -839,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492168.7949977426</v>
+        <v>492169</v>
       </c>
       <c r="R3" t="n">
-        <v>6609325.137273833</v>
+        <v>6609325</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
@@ -872,19 +852,9 @@
           <t>1980-08-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1980-08-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -919,6 +889,113 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>79459471</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99879</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Björknäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>492158</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6609381</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1980-08-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1980-08-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Björknäs. NV del av udden nära stranden. Under åren 1980-1993 iakttagen på ytterligare 14 lokaler i  "Nora socken".</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lars Asklund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lars Asklund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51036-2022 artfynd.xlsx
+++ b/artfynd/A 51036-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16612609</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80476233</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,8 +1011,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79459471</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>